--- a/data/trans_camb/IP18A01-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A01-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-2.137738530192633</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.283215046701445</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.212060133627075</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.405161340235131</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-2.156856509591154</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-4.098887875986525</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-7.170705135597894</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.41555869479189</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.593296025348705</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.69072349952898</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-5.062032746665153</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-9.023988492563555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>1.837336072688157</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.393968352663137</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.395966508343697</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>18.42637037063695</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.9175585899536166</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.149990147251582</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.2001121766267981</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.5881672718395429</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.230787581827397</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1466026094229507</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2126155723644593</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.4040544134184494</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5249633410824069</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.5376186369667327</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4242194755004766</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8485405416279509</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.2395473569122533</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.5978355541280366</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.3445905034965902</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2.424293534371593</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1146315362754839</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.7330197794182249</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.2839749547391038</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.292164586051204</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.483872352113369</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.203974430257645</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.9236735203381058</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-4.835880948388972</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-4.054335562863035</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.358483792544273</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.744243627998461</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.947936593786778</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.510243267594527</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-7.912281614823854</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>4.841191339292339</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.292969647825541</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.549061792275994</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.162641276796823</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.549483436591672</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.8406298216712084</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.03842264619928314</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.5807424865000912</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1616372290486787</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.5668654758268299</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1116146669554001</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.584357166905494</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.4294545475311192</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.9241374125833192</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.3380110100191128</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8965173212269001</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2563037441026161</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8330820956066047</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.9069415938407729</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.3781197375965138</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.8731934559442471</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.4366870387080894</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7001610700636898</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.101339845304284</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0.8596819735835384</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.132918160661223</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.4959946463252179</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.04061388381189635</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.2117525508769438</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.521316722130161</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.788573220230226</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.532174598385106</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.888793764243468</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.939424427879775</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.744791867172263</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-8.042499885161575</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>6.702508461048892</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.423903109219809</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.70795305770826</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>13.82043856681647</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.510216497364333</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>4.165035885622802</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.0838153007744864</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.4029417730701043</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.04107025039241771</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.00336298464090566</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.01900099642758353</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.2262429889585717</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3623738190719799</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8054117589092012</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.4496157296464128</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.6582457862804246</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.2938581847748069</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6712330596169135</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.917782118228806</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.6441113246464532</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.6478175050800242</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.558020202816662</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.5030729148526583</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4477831663562319</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-4.655454689619279</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-13.16170407429614</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.006554967753049</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-8.582467705927153</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-3.462440046663723</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-11.04353635429925</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-13.16119297307675</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-20.07133247902558</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.935013349906905</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-15.67780387583471</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-9.163908895857606</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-15.7273919206297</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.333682374706758</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-7.870409728408482</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>6.624218475160798</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-2.296222950646163</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>2.141034756403184</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-6.816851473567649</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.3537121533305893</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.1975436541710055</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.8449367496431097</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2930097100838749</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.9345615640599793</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.700699384293281</v>
+      </c>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="n">
+        <v>-0.7315664492899466</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.6222327311917256</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1208,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.3897265694323548</v>
+      </c>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="n">
+        <v>1.335451427653305</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.1857758125853085</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.288786831146399</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.6503859085492076</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1236,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.064651766601708</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-6.117095312737042</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.7219636625625664</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-3.269588068873353</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.8971364125088046</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-4.91124307151685</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1262,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.854782853176644</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-8.594006602172364</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.167982930468555</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-7.00759280928547</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.824958301548485</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-7.272035276072542</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1288,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.376515762570612</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-2.188836043582764</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.934234103266114</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>3.163574988839193</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.948032928185236</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-2.044788623465215</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1314,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1075314210779121</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.6178357773708817</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.0716255344936317</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.3243736563912731</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.08982411170458153</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.4917290616157575</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1340,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.3445528501747758</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.8022641669634184</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.2874533172406576</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.6410669181304451</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2568208376068972</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.6928150605487688</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1366,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.1563738726489773</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.2259146952983787</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2261770048535759</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.3470303909599218</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.1062124263427664</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.2024325233335523</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1394,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
